--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/122.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/122.xlsx
@@ -426,13 +426,13 @@
         <v>-6.414216311999493</v>
       </c>
       <c r="E2">
-        <v>-24.06707079413855</v>
+        <v>-28.07848363961311</v>
       </c>
       <c r="F2">
-        <v>-2.952878114537294</v>
+        <v>-3.124582938156979</v>
       </c>
       <c r="G2">
-        <v>-12.7557251251215</v>
+        <v>-15.60867050722692</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.617761884952009</v>
       </c>
       <c r="E3">
-        <v>-24.4501434673954</v>
+        <v>-28.02488462125832</v>
       </c>
       <c r="F3">
-        <v>-2.771678543746722</v>
+        <v>-3.097603011847799</v>
       </c>
       <c r="G3">
-        <v>-12.71901779618206</v>
+        <v>-15.60213880087794</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.840070224496076</v>
       </c>
       <c r="E4">
-        <v>-23.9608871356067</v>
+        <v>-28.22052828381171</v>
       </c>
       <c r="F4">
-        <v>-2.792850786194875</v>
+        <v>-3.108746210150258</v>
       </c>
       <c r="G4">
-        <v>-12.64667906560344</v>
+        <v>-15.48657593246583</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.050426715348536</v>
       </c>
       <c r="E5">
-        <v>-24.39313903658685</v>
+        <v>-29.15291843962099</v>
       </c>
       <c r="F5">
-        <v>-2.823032352515875</v>
+        <v>-3.129845556266964</v>
       </c>
       <c r="G5">
-        <v>-12.67268340081442</v>
+        <v>-15.4527140174174</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.237652331852367</v>
       </c>
       <c r="E6">
-        <v>-24.87404939077942</v>
+        <v>-29.08830164400554</v>
       </c>
       <c r="F6">
-        <v>-2.888599289182261</v>
+        <v>-3.229246331133293</v>
       </c>
       <c r="G6">
-        <v>-12.20583357941193</v>
+        <v>-15.2028886641146</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.38239067075431</v>
       </c>
       <c r="E7">
-        <v>-25.49981204305534</v>
+        <v>-29.99860869631643</v>
       </c>
       <c r="F7">
-        <v>-2.802516177050739</v>
+        <v>-3.264519871879302</v>
       </c>
       <c r="G7">
-        <v>-12.0501882808831</v>
+        <v>-15.21574020189806</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.471458770672307</v>
       </c>
       <c r="E8">
-        <v>-25.18705298571559</v>
+        <v>-29.6066919133226</v>
       </c>
       <c r="F8">
-        <v>-2.658112686292521</v>
+        <v>-2.93673571895894</v>
       </c>
       <c r="G8">
-        <v>-11.87137578467044</v>
+        <v>-14.81076116607901</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.486922675604397</v>
       </c>
       <c r="E9">
-        <v>-26.57224072907783</v>
+        <v>-30.49117760684175</v>
       </c>
       <c r="F9">
-        <v>-2.648129202353981</v>
+        <v>-3.080319125988387</v>
       </c>
       <c r="G9">
-        <v>-11.89543351910433</v>
+        <v>-14.54111061081429</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.41599847503014</v>
       </c>
       <c r="E10">
-        <v>-26.42002966073201</v>
+        <v>-30.78131014380217</v>
       </c>
       <c r="F10">
-        <v>-2.756187244946968</v>
+        <v>-3.007058312884799</v>
       </c>
       <c r="G10">
-        <v>-11.51000325469468</v>
+        <v>-14.506565068112</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.255591835641605</v>
       </c>
       <c r="E11">
-        <v>-27.10484361406795</v>
+        <v>-31.24788108504945</v>
       </c>
       <c r="F11">
-        <v>-2.700175526271874</v>
+        <v>-3.017353262966791</v>
       </c>
       <c r="G11">
-        <v>-11.26795271759087</v>
+        <v>-14.09484410630223</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.008699038068985</v>
       </c>
       <c r="E12">
-        <v>-27.69182441494218</v>
+        <v>-31.71800008568174</v>
       </c>
       <c r="F12">
-        <v>-2.697624983038655</v>
+        <v>-3.02741047160418</v>
       </c>
       <c r="G12">
-        <v>-11.31986538219218</v>
+        <v>-13.96394182513391</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.687674381589056</v>
       </c>
       <c r="E13">
-        <v>-28.3785720266794</v>
+        <v>-31.73719402276325</v>
       </c>
       <c r="F13">
-        <v>-2.785372285282401</v>
+        <v>-2.996576980137176</v>
       </c>
       <c r="G13">
-        <v>-11.09698952485182</v>
+        <v>-13.6652511643987</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.320091132710437</v>
       </c>
       <c r="E14">
-        <v>-29.05136740999898</v>
+        <v>-32.2215709238087</v>
       </c>
       <c r="F14">
-        <v>-2.459750999650749</v>
+        <v>-2.979248362438013</v>
       </c>
       <c r="G14">
-        <v>-10.30988745961686</v>
+        <v>-13.36341217485565</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.931600740146037</v>
       </c>
       <c r="E15">
-        <v>-29.79566966213669</v>
+        <v>-33.5311716432719</v>
       </c>
       <c r="F15">
-        <v>-2.140436903424012</v>
+        <v>-2.678449106031249</v>
       </c>
       <c r="G15">
-        <v>-10.16779884507134</v>
+        <v>-12.83348652929344</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.546027881612426</v>
       </c>
       <c r="E16">
-        <v>-30.29885784420999</v>
+        <v>-33.70029429779937</v>
       </c>
       <c r="F16">
-        <v>-2.281486334568295</v>
+        <v>-2.617859829088284</v>
       </c>
       <c r="G16">
-        <v>-9.869257158885407</v>
+        <v>-12.45962662154354</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.18971735743524</v>
       </c>
       <c r="E17">
-        <v>-30.93369102992328</v>
+        <v>-34.39858725401914</v>
       </c>
       <c r="F17">
-        <v>-1.983660088770177</v>
+        <v>-2.732214292309951</v>
       </c>
       <c r="G17">
-        <v>-9.325152446778493</v>
+        <v>-12.78544389242753</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.875908926660745</v>
       </c>
       <c r="E18">
-        <v>-31.85928394624705</v>
+        <v>-35.08460125296711</v>
       </c>
       <c r="F18">
-        <v>-1.904818564473929</v>
+        <v>-2.604370694301097</v>
       </c>
       <c r="G18">
-        <v>-9.210495012571373</v>
+        <v>-11.88802451818744</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.610114801925252</v>
       </c>
       <c r="E19">
-        <v>-32.40845651763124</v>
+        <v>-35.92072963679535</v>
       </c>
       <c r="F19">
-        <v>-1.818525875389499</v>
+        <v>-2.321666295441085</v>
       </c>
       <c r="G19">
-        <v>-8.812835592939658</v>
+        <v>-12.10118723491557</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.398824977647445</v>
       </c>
       <c r="E20">
-        <v>-32.82943931104331</v>
+        <v>-36.59520281973478</v>
       </c>
       <c r="F20">
-        <v>-1.564675169903799</v>
+        <v>-2.259788907186767</v>
       </c>
       <c r="G20">
-        <v>-8.522729176787784</v>
+        <v>-12.04816884810414</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.236596516659615</v>
       </c>
       <c r="E21">
-        <v>-33.87222687044859</v>
+        <v>-36.7315959283718</v>
       </c>
       <c r="F21">
-        <v>-1.626820949196623</v>
+        <v>-2.197883354440755</v>
       </c>
       <c r="G21">
-        <v>-8.616516931915337</v>
+        <v>-11.7128470009769</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.113178316994133</v>
       </c>
       <c r="E22">
-        <v>-34.4988091765199</v>
+        <v>-37.2617036241837</v>
       </c>
       <c r="F22">
-        <v>-1.42392892122894</v>
+        <v>-1.881174473695823</v>
       </c>
       <c r="G22">
-        <v>-8.599931098763589</v>
+        <v>-11.73281952221533</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.02289035183772</v>
       </c>
       <c r="E23">
-        <v>-34.25279076910519</v>
+        <v>-38.2474075044853</v>
       </c>
       <c r="F23">
-        <v>-1.120513680564135</v>
+        <v>-1.966012549620937</v>
       </c>
       <c r="G23">
-        <v>-8.396355721917185</v>
+        <v>-11.51845838800198</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.953541903677109</v>
       </c>
       <c r="E24">
-        <v>-34.94692658618592</v>
+        <v>-38.01292312036812</v>
       </c>
       <c r="F24">
-        <v>-1.29643240916186</v>
+        <v>-1.609600847627227</v>
       </c>
       <c r="G24">
-        <v>-8.411723274310482</v>
+        <v>-11.46235788329349</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.894921872898807</v>
       </c>
       <c r="E25">
-        <v>-35.85663135145379</v>
+        <v>-38.18421717818227</v>
       </c>
       <c r="F25">
-        <v>-0.9307926943009638</v>
+        <v>-1.520699629591381</v>
       </c>
       <c r="G25">
-        <v>-8.188873901334443</v>
+        <v>-11.80074529559009</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.844926389547692</v>
       </c>
       <c r="E26">
-        <v>-35.60252735369838</v>
+        <v>-38.64551923992162</v>
       </c>
       <c r="F26">
-        <v>-0.9940194930544417</v>
+        <v>-1.534277399690668</v>
       </c>
       <c r="G26">
-        <v>-8.384153051059432</v>
+        <v>-11.74227775082102</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.799696055742728</v>
       </c>
       <c r="E27">
-        <v>-35.59561916659968</v>
+        <v>-38.46936839373426</v>
       </c>
       <c r="F27">
-        <v>-0.8904023281078628</v>
+        <v>-1.533211290843265</v>
       </c>
       <c r="G27">
-        <v>-8.168570325542092</v>
+        <v>-11.54509172686542</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.760455775982365</v>
       </c>
       <c r="E28">
-        <v>-34.92929497263705</v>
+        <v>-38.43033294778814</v>
       </c>
       <c r="F28">
-        <v>-1.048678487760764</v>
+        <v>-1.416990515863092</v>
       </c>
       <c r="G28">
-        <v>-8.372973338773313</v>
+        <v>-12.07817232232656</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.734144480693713</v>
       </c>
       <c r="E29">
-        <v>-35.38306618210166</v>
+        <v>-38.50843780323543</v>
       </c>
       <c r="F29">
-        <v>-0.656303214974514</v>
+        <v>-1.517250307726124</v>
       </c>
       <c r="G29">
-        <v>-8.583841847442731</v>
+        <v>-11.8413027889917</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.724263953177038</v>
       </c>
       <c r="E30">
-        <v>-35.35504172070519</v>
+        <v>-38.34325265685764</v>
       </c>
       <c r="F30">
-        <v>-0.6005333795810374</v>
+        <v>-1.32353659058146</v>
       </c>
       <c r="G30">
-        <v>-8.322669599304088</v>
+        <v>-11.73018763851161</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.737776723158487</v>
       </c>
       <c r="E31">
-        <v>-34.5497001674181</v>
+        <v>-37.97141059913981</v>
       </c>
       <c r="F31">
-        <v>-0.8392034240430337</v>
+        <v>-1.338183782997761</v>
       </c>
       <c r="G31">
-        <v>-8.557986486781022</v>
+        <v>-12.082509136983</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.782352440077728</v>
       </c>
       <c r="E32">
-        <v>-34.51572755541255</v>
+        <v>-37.78120563386964</v>
       </c>
       <c r="F32">
-        <v>-0.8967865556812386</v>
+        <v>-1.568541160572664</v>
       </c>
       <c r="G32">
-        <v>-8.725877493259622</v>
+        <v>-12.22141300671974</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.858432005245353</v>
       </c>
       <c r="E33">
-        <v>-34.79544233791834</v>
+        <v>-37.58670541100319</v>
       </c>
       <c r="F33">
-        <v>-0.8840644891090437</v>
+        <v>-1.547302648732287</v>
       </c>
       <c r="G33">
-        <v>-8.97807816298684</v>
+        <v>-12.09830043920533</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.969722742502269</v>
       </c>
       <c r="E34">
-        <v>-34.21450931408135</v>
+        <v>-37.20863443728781</v>
       </c>
       <c r="F34">
-        <v>-0.7912276975424976</v>
+        <v>-1.308441251400244</v>
       </c>
       <c r="G34">
-        <v>-9.776061991409385</v>
+        <v>-12.34092701123297</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.119130483947874</v>
       </c>
       <c r="E35">
-        <v>-33.0172962625405</v>
+        <v>-36.97417269554068</v>
       </c>
       <c r="F35">
-        <v>-0.87687011821573</v>
+        <v>-1.526175966491289</v>
       </c>
       <c r="G35">
-        <v>-9.628878447278927</v>
+        <v>-12.97599889366798</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.302053561905708</v>
       </c>
       <c r="E36">
-        <v>-33.4669918453982</v>
+        <v>-36.34052597001741</v>
       </c>
       <c r="F36">
-        <v>-0.9022869152358273</v>
+        <v>-1.535096655052037</v>
       </c>
       <c r="G36">
-        <v>-9.487435389113566</v>
+        <v>-12.55853579062035</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.518946657345744</v>
       </c>
       <c r="E37">
-        <v>-32.54843164920833</v>
+        <v>-36.01289766827347</v>
       </c>
       <c r="F37">
-        <v>-0.6113029841848338</v>
+        <v>-1.347164942378913</v>
       </c>
       <c r="G37">
-        <v>-9.451426585282913</v>
+        <v>-12.36057840955409</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.768816176879462</v>
       </c>
       <c r="E38">
-        <v>-32.52520284178599</v>
+        <v>-35.47762524785582</v>
       </c>
       <c r="F38">
-        <v>-0.7739222741306131</v>
+        <v>-1.512959364579623</v>
       </c>
       <c r="G38">
-        <v>-9.582090507172408</v>
+        <v>-12.81180245601121</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.041994781813194</v>
       </c>
       <c r="E39">
-        <v>-31.92258522016327</v>
+        <v>-34.71097271225326</v>
       </c>
       <c r="F39">
-        <v>-0.6991198692904149</v>
+        <v>-1.31006733661194</v>
       </c>
       <c r="G39">
-        <v>-9.597616965751589</v>
+        <v>-12.83493985878518</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.335838606572963</v>
       </c>
       <c r="E40">
-        <v>-31.53747246936597</v>
+        <v>-34.45776535235137</v>
       </c>
       <c r="F40">
-        <v>-0.7226935488392833</v>
+        <v>-1.304747561151161</v>
       </c>
       <c r="G40">
-        <v>-9.789059193196563</v>
+        <v>-12.63045077136993</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.646280783731883</v>
       </c>
       <c r="E41">
-        <v>-30.65826471230276</v>
+        <v>-34.06975890666317</v>
       </c>
       <c r="F41">
-        <v>-0.5935021970660751</v>
+        <v>-1.167515246998978</v>
       </c>
       <c r="G41">
-        <v>-9.79638543047497</v>
+        <v>-12.80524095475237</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.961269211336393</v>
       </c>
       <c r="E42">
-        <v>-29.7701132190744</v>
+        <v>-33.52569218972263</v>
       </c>
       <c r="F42">
-        <v>-0.5086467254255022</v>
+        <v>-1.1609230992075</v>
       </c>
       <c r="G42">
-        <v>-9.615255552384827</v>
+        <v>-12.92436431489197</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.280553971923158</v>
       </c>
       <c r="E43">
-        <v>-29.4078534123568</v>
+        <v>-32.89452480371855</v>
       </c>
       <c r="F43">
-        <v>-0.3582334291599735</v>
+        <v>-1.099555985273307</v>
       </c>
       <c r="G43">
-        <v>-9.690381762307508</v>
+        <v>-13.0423356051839</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.604087892053808</v>
       </c>
       <c r="E44">
-        <v>-29.35918590219637</v>
+        <v>-32.55119401835302</v>
       </c>
       <c r="F44">
-        <v>-0.4222007883715542</v>
+        <v>-0.9365150563195028</v>
       </c>
       <c r="G44">
-        <v>-9.903633863765201</v>
+        <v>-12.78754277829943</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.924410353144246</v>
       </c>
       <c r="E45">
-        <v>-28.21782478482913</v>
+        <v>-31.97250032491282</v>
       </c>
       <c r="F45">
-        <v>-0.4893291975922177</v>
+        <v>-1.045665715516783</v>
       </c>
       <c r="G45">
-        <v>-9.706245896531694</v>
+        <v>-12.93565658572642</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.245980229552945</v>
       </c>
       <c r="E46">
-        <v>-28.05955008978704</v>
+        <v>-31.69271308682291</v>
       </c>
       <c r="F46">
-        <v>-0.2526795412256493</v>
+        <v>-0.9203726607411489</v>
       </c>
       <c r="G46">
-        <v>-10.27291859757982</v>
+        <v>-12.99155183661148</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.572944711595469</v>
       </c>
       <c r="E47">
-        <v>-27.37365383116326</v>
+        <v>-30.92491937577042</v>
       </c>
       <c r="F47">
-        <v>-0.2428799548505312</v>
+        <v>-1.146342176183423</v>
       </c>
       <c r="G47">
-        <v>-9.573099065487748</v>
+        <v>-13.07585156822348</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.901199858918252</v>
       </c>
       <c r="E48">
-        <v>-26.79538581427979</v>
+        <v>-30.39814916530217</v>
       </c>
       <c r="F48">
-        <v>-0.08405872944658759</v>
+        <v>-1.029873719349813</v>
       </c>
       <c r="G48">
-        <v>-9.793147716937563</v>
+        <v>-13.0362243381184</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.236074481590331</v>
       </c>
       <c r="E49">
-        <v>-26.51447551463598</v>
+        <v>-30.10141864171257</v>
       </c>
       <c r="F49">
-        <v>-0.07444304063489092</v>
+        <v>-0.9440780507070623</v>
       </c>
       <c r="G49">
-        <v>-9.716300023334462</v>
+        <v>-12.96371345917175</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.582113734086377</v>
       </c>
       <c r="E50">
-        <v>-25.44472768522604</v>
+        <v>-29.97098953334365</v>
       </c>
       <c r="F50">
-        <v>-0.1010825079415202</v>
+        <v>-0.8497825041441862</v>
       </c>
       <c r="G50">
-        <v>-9.833119243778723</v>
+        <v>-13.02772947826463</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.935401314677925</v>
       </c>
       <c r="E51">
-        <v>-25.16225506204958</v>
+        <v>-28.93736760532989</v>
       </c>
       <c r="F51">
-        <v>-0.007401609991521335</v>
+        <v>-0.9795255486076587</v>
       </c>
       <c r="G51">
-        <v>-9.916892598649982</v>
+        <v>-12.97729993806492</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.297956269591499</v>
       </c>
       <c r="E52">
-        <v>-24.55322964970601</v>
+        <v>-29.06830843126168</v>
       </c>
       <c r="F52">
-        <v>-0.3182183134003406</v>
+        <v>-0.9231990503195008</v>
       </c>
       <c r="G52">
-        <v>-9.812166801060677</v>
+        <v>-13.33179977550115</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.670449666325782</v>
       </c>
       <c r="E53">
-        <v>-23.82922628230769</v>
+        <v>-28.58766525703556</v>
       </c>
       <c r="F53">
-        <v>-0.06196451407911917</v>
+        <v>-0.7805591537618427</v>
       </c>
       <c r="G53">
-        <v>-9.939397687225947</v>
+        <v>-13.43809477167607</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.04557601670471</v>
       </c>
       <c r="E54">
-        <v>-23.85609824706921</v>
+        <v>-27.69078286592042</v>
       </c>
       <c r="F54">
-        <v>0.06318523313583013</v>
+        <v>-0.7733540140922927</v>
       </c>
       <c r="G54">
-        <v>-9.872620673153307</v>
+        <v>-13.22296559089761</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.4176828516372</v>
       </c>
       <c r="E55">
-        <v>-23.40612189882303</v>
+        <v>-27.3800525649361</v>
       </c>
       <c r="F55">
-        <v>-0.09305231433878182</v>
+        <v>-0.8675170218707208</v>
       </c>
       <c r="G55">
-        <v>-10.02527654906018</v>
+        <v>-13.45945441149545</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.77966957820805</v>
       </c>
       <c r="E56">
-        <v>-22.62043618696623</v>
+        <v>-27.36815626371795</v>
       </c>
       <c r="F56">
-        <v>-0.1439206998098939</v>
+        <v>-0.6655113470240334</v>
       </c>
       <c r="G56">
-        <v>-10.14166539858434</v>
+        <v>-13.28039031382181</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.11955567047731</v>
       </c>
       <c r="E57">
-        <v>-22.13031491664206</v>
+        <v>-26.55092067344971</v>
       </c>
       <c r="F57">
-        <v>0.0875284660018992</v>
+        <v>-0.8923796410983451</v>
       </c>
       <c r="G57">
-        <v>-10.28938194054662</v>
+        <v>-13.2836180957226</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.42485087104216</v>
       </c>
       <c r="E58">
-        <v>-21.80439158536201</v>
+        <v>-26.20008167817946</v>
       </c>
       <c r="F58">
-        <v>0.1418594272167132</v>
+        <v>-0.8933711968794962</v>
       </c>
       <c r="G58">
-        <v>-10.16410427624952</v>
+        <v>-13.50203630349433</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.68342714759406</v>
       </c>
       <c r="E59">
-        <v>-21.45875580672657</v>
+        <v>-25.85613502034888</v>
       </c>
       <c r="F59">
-        <v>-0.2840266204823882</v>
+        <v>-0.8456067040666739</v>
       </c>
       <c r="G59">
-        <v>-10.40161936596453</v>
+        <v>-13.52143775562723</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.88369454584207</v>
       </c>
       <c r="E60">
-        <v>-21.33167324064932</v>
+        <v>-25.86056386792838</v>
       </c>
       <c r="F60">
-        <v>-0.2193468653044</v>
+        <v>-0.819882582740138</v>
       </c>
       <c r="G60">
-        <v>-10.3772206453401</v>
+        <v>-13.59290250218347</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.0118293023657</v>
       </c>
       <c r="E61">
-        <v>-21.21203095736667</v>
+        <v>-26.07172661090605</v>
       </c>
       <c r="F61">
-        <v>-0.2998401542018308</v>
+        <v>-0.8130435814626253</v>
       </c>
       <c r="G61">
-        <v>-10.1297672979162</v>
+        <v>-13.49642989462357</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.05662502231502</v>
       </c>
       <c r="E62">
-        <v>-20.13315825283127</v>
+        <v>-25.37055580945441</v>
       </c>
       <c r="F62">
-        <v>-0.2407850136888512</v>
+        <v>-0.940224485549239</v>
       </c>
       <c r="G62">
-        <v>-10.42034050098911</v>
+        <v>-13.4325165024424</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.01601926056756</v>
       </c>
       <c r="E63">
-        <v>-21.00741185933008</v>
+        <v>-25.42891425399125</v>
       </c>
       <c r="F63">
-        <v>-0.3183955840245397</v>
+        <v>-0.9325455197252875</v>
       </c>
       <c r="G63">
-        <v>-10.59177048064919</v>
+        <v>-13.54448411839886</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.88679712701361</v>
       </c>
       <c r="E64">
-        <v>-20.61707098529092</v>
+        <v>-25.09591291783721</v>
       </c>
       <c r="F64">
-        <v>-0.441921731130002</v>
+        <v>-0.9172298348149275</v>
       </c>
       <c r="G64">
-        <v>-10.41337180262894</v>
+        <v>-13.49812158339414</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.66982480831531</v>
       </c>
       <c r="E65">
-        <v>-20.3624258348916</v>
+        <v>-25.20563331456906</v>
       </c>
       <c r="F65">
-        <v>-0.7387622197187881</v>
+        <v>-1.075158908526056</v>
       </c>
       <c r="G65">
-        <v>-10.4896931194913</v>
+        <v>-13.78699978715094</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.37847312465856</v>
       </c>
       <c r="E66">
-        <v>-19.7733347651298</v>
+        <v>-25.04803336215411</v>
       </c>
       <c r="F66">
-        <v>-0.5560591620921347</v>
+        <v>-1.234386033957371</v>
       </c>
       <c r="G66">
-        <v>-10.49047109769303</v>
+        <v>-13.68478172780763</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.02046673189842</v>
       </c>
       <c r="E67">
-        <v>-20.52510220666914</v>
+        <v>-24.84650268339076</v>
       </c>
       <c r="F67">
-        <v>-0.8854047875667733</v>
+        <v>-1.3278391308716</v>
       </c>
       <c r="G67">
-        <v>-10.53247198894976</v>
+        <v>-13.70943039462028</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.60509861846996</v>
       </c>
       <c r="E68">
-        <v>-19.9110728305471</v>
+        <v>-25.23117390797232</v>
       </c>
       <c r="F68">
-        <v>-0.7015560978220482</v>
+        <v>-1.589724171797053</v>
       </c>
       <c r="G68">
-        <v>-10.73577259051641</v>
+        <v>-13.12109348356316</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.15321385528873</v>
       </c>
       <c r="E69">
-        <v>-19.75284342024509</v>
+        <v>-24.76831405117432</v>
       </c>
       <c r="F69">
-        <v>-0.9920686878208489</v>
+        <v>-1.445714155555164</v>
       </c>
       <c r="G69">
-        <v>-10.10289891031947</v>
+        <v>-13.52521508808753</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.675720187586517</v>
       </c>
       <c r="E70">
-        <v>-20.02449299054321</v>
+        <v>-24.90479320081749</v>
       </c>
       <c r="F70">
-        <v>-1.141487114835615</v>
+        <v>-1.638314546910466</v>
       </c>
       <c r="G70">
-        <v>-10.19268421589005</v>
+        <v>-13.06704882763456</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.181480964350776</v>
       </c>
       <c r="E71">
-        <v>-19.61390078074174</v>
+        <v>-24.76886199652925</v>
       </c>
       <c r="F71">
-        <v>-1.050460306044186</v>
+        <v>-1.74237406005014</v>
       </c>
       <c r="G71">
-        <v>-9.896211620666154</v>
+        <v>-13.01762900382432</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.689539487631905</v>
       </c>
       <c r="E72">
-        <v>-20.17203520218712</v>
+        <v>-24.84019451909807</v>
       </c>
       <c r="F72">
-        <v>-1.444466634246548</v>
+        <v>-1.644151223630592</v>
       </c>
       <c r="G72">
-        <v>-10.12925416335761</v>
+        <v>-12.96085645837136</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.207693472798606</v>
       </c>
       <c r="E73">
-        <v>-19.72995198413631</v>
+        <v>-24.38805808875024</v>
       </c>
       <c r="F73">
-        <v>-1.377252074815994</v>
+        <v>-1.908589292891472</v>
       </c>
       <c r="G73">
-        <v>-10.08613099716306</v>
+        <v>-13.44215681105276</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.741114778365736</v>
       </c>
       <c r="E74">
-        <v>-19.62355095885209</v>
+        <v>-24.88549737307081</v>
       </c>
       <c r="F74">
-        <v>-1.571472752811171</v>
+        <v>-1.867664629723566</v>
       </c>
       <c r="G74">
-        <v>-9.599735714896722</v>
+        <v>-13.01502029393937</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.305127327471435</v>
       </c>
       <c r="E75">
-        <v>-19.66456987641357</v>
+        <v>-25.34916329824217</v>
       </c>
       <c r="F75">
-        <v>-1.548844240468897</v>
+        <v>-1.987632110466601</v>
       </c>
       <c r="G75">
-        <v>-9.602198760777942</v>
+        <v>-12.77964712718827</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.904455977332299</v>
       </c>
       <c r="E76">
-        <v>-20.33554481318207</v>
+        <v>-24.76302932200737</v>
       </c>
       <c r="F76">
-        <v>-1.809949787668315</v>
+        <v>-2.100639648291315</v>
       </c>
       <c r="G76">
-        <v>-9.276040503703404</v>
+        <v>-12.63652231188896</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.541085542826198</v>
       </c>
       <c r="E77">
-        <v>-20.68291046888844</v>
+        <v>-25.09113990623313</v>
       </c>
       <c r="F77">
-        <v>-1.952409928499566</v>
+        <v>-2.306454156456075</v>
       </c>
       <c r="G77">
-        <v>-9.41773516332975</v>
+        <v>-12.55134528570905</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.223988397367744</v>
       </c>
       <c r="E78">
-        <v>-20.29033252868949</v>
+        <v>-25.25423742609338</v>
       </c>
       <c r="F78">
-        <v>-2.026970450058147</v>
+        <v>-2.260078007410344</v>
       </c>
       <c r="G78">
-        <v>-9.141043077703003</v>
+        <v>-12.42549820757919</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.951406623579221</v>
       </c>
       <c r="E79">
-        <v>-20.65609284581502</v>
+        <v>-25.69582251200334</v>
       </c>
       <c r="F79">
-        <v>-1.955174190522708</v>
+        <v>-2.469482659898837</v>
       </c>
       <c r="G79">
-        <v>-9.256207025377631</v>
+        <v>-12.60449609434205</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.720630754009508</v>
       </c>
       <c r="E80">
-        <v>-21.90237870593998</v>
+        <v>-25.73702256852513</v>
       </c>
       <c r="F80">
-        <v>-2.034948456514509</v>
+        <v>-2.422857172264864</v>
       </c>
       <c r="G80">
-        <v>-8.683601826723129</v>
+        <v>-12.21228583266797</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.535809866599439</v>
       </c>
       <c r="E81">
-        <v>-21.82130090730665</v>
+        <v>-26.42173236695889</v>
       </c>
       <c r="F81">
-        <v>-2.227936523814321</v>
+        <v>-2.47089502632061</v>
       </c>
       <c r="G81">
-        <v>-8.503067846830053</v>
+        <v>-12.02488909187199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.393133253691802</v>
       </c>
       <c r="E82">
-        <v>-21.82963782795477</v>
+        <v>-26.34142893738088</v>
       </c>
       <c r="F82">
-        <v>-1.918377282122951</v>
+        <v>-2.568378130649459</v>
       </c>
       <c r="G82">
-        <v>-8.90830510520116</v>
+        <v>-12.46978668580356</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.291326606704376</v>
       </c>
       <c r="E83">
-        <v>-22.43405325375854</v>
+        <v>-27.0901713582831</v>
       </c>
       <c r="F83">
-        <v>-2.241940903126049</v>
+        <v>-2.572334413365229</v>
       </c>
       <c r="G83">
-        <v>-8.418231806840689</v>
+        <v>-12.18909215061984</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.235158928772466</v>
       </c>
       <c r="E84">
-        <v>-23.34922162291666</v>
+        <v>-27.79365168147866</v>
       </c>
       <c r="F84">
-        <v>-2.715496181386651</v>
+        <v>-2.501162742851502</v>
       </c>
       <c r="G84">
-        <v>-8.427600650716828</v>
+        <v>-12.21393117380099</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.222147978740725</v>
       </c>
       <c r="E85">
-        <v>-24.15380918528147</v>
+        <v>-28.42293295805854</v>
       </c>
       <c r="F85">
-        <v>-2.267196996870004</v>
+        <v>-2.658079551596409</v>
       </c>
       <c r="G85">
-        <v>-8.3215241505475</v>
+        <v>-12.05795151017269</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.25368125067276</v>
       </c>
       <c r="E86">
-        <v>-24.70836611226078</v>
+        <v>-29.19801298378938</v>
       </c>
       <c r="F86">
-        <v>-2.440609085706857</v>
+        <v>-2.805838758703368</v>
       </c>
       <c r="G86">
-        <v>-8.173860577313848</v>
+        <v>-12.20625401869542</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.334248712212622</v>
       </c>
       <c r="E87">
-        <v>-26.25771103840107</v>
+        <v>-30.20012126118375</v>
       </c>
       <c r="F87">
-        <v>-2.452263386696844</v>
+        <v>-2.872741023623067</v>
       </c>
       <c r="G87">
-        <v>-8.531862971930634</v>
+        <v>-12.05636575885938</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.460469895028773</v>
       </c>
       <c r="E88">
-        <v>-26.85745307902892</v>
+        <v>-30.6134803686039</v>
       </c>
       <c r="F88">
-        <v>-2.533884911996887</v>
+        <v>-2.778327848888994</v>
       </c>
       <c r="G88">
-        <v>-8.172976661654863</v>
+        <v>-11.83666140414565</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.634721731502181</v>
       </c>
       <c r="E89">
-        <v>-28.11611525861685</v>
+        <v>-31.78291123210769</v>
       </c>
       <c r="F89">
-        <v>-2.546744487557947</v>
+        <v>-3.025204529210525</v>
       </c>
       <c r="G89">
-        <v>-7.697552527305667</v>
+        <v>-12.02591536098916</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.859116691763467</v>
       </c>
       <c r="E90">
-        <v>-29.27317659536869</v>
+        <v>-32.76056574986065</v>
       </c>
       <c r="F90">
-        <v>-2.407964783097335</v>
+        <v>-3.053207489262162</v>
       </c>
       <c r="G90">
-        <v>-8.29544698333466</v>
+        <v>-12.09965114178535</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.125334306297937</v>
       </c>
       <c r="E91">
-        <v>-30.55391734998101</v>
+        <v>-33.95354241396732</v>
       </c>
       <c r="F91">
-        <v>-2.639875349552487</v>
+        <v>-2.900250276702636</v>
       </c>
       <c r="G91">
-        <v>-8.240412474289817</v>
+        <v>-11.97238383961915</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.430640405486606</v>
       </c>
       <c r="E92">
-        <v>-31.85267237419585</v>
+        <v>-35.42391754612485</v>
       </c>
       <c r="F92">
-        <v>-2.837208203879983</v>
+        <v>-3.22033889645099</v>
       </c>
       <c r="G92">
-        <v>-8.34351279401934</v>
+        <v>-12.42073433254818</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.769424150571709</v>
       </c>
       <c r="E93">
-        <v>-32.77479647942975</v>
+        <v>-35.99582305702755</v>
       </c>
       <c r="F93">
-        <v>-2.970369092247406</v>
+        <v>-3.373682128220221</v>
       </c>
       <c r="G93">
-        <v>-8.801970382479769</v>
+        <v>-12.53517327074971</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.124573784371754</v>
       </c>
       <c r="E94">
-        <v>-34.38877631508152</v>
+        <v>-37.31728158567984</v>
       </c>
       <c r="F94">
-        <v>-2.887477679718871</v>
+        <v>-3.521036263667211</v>
       </c>
       <c r="G94">
-        <v>-9.160204515284306</v>
+        <v>-12.41445422766019</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.486725108039064</v>
       </c>
       <c r="E95">
-        <v>-36.26146334231749</v>
+        <v>-38.89427963834797</v>
       </c>
       <c r="F95">
-        <v>-3.09214407066335</v>
+        <v>-3.445931504724991</v>
       </c>
       <c r="G95">
-        <v>-9.170136151902119</v>
+        <v>-12.40970359481133</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.844214500625334</v>
       </c>
       <c r="E96">
-        <v>-37.75843646655908</v>
+        <v>-40.65396312519653</v>
       </c>
       <c r="F96">
-        <v>-3.238031167439982</v>
+        <v>-3.719354046836635</v>
       </c>
       <c r="G96">
-        <v>-9.089908391303421</v>
+        <v>-12.64986712095776</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.179445217080508</v>
       </c>
       <c r="E97">
-        <v>-39.47245708575129</v>
+        <v>-42.24193819885926</v>
       </c>
       <c r="F97">
-        <v>-3.312317499388236</v>
+        <v>-3.981928289441216</v>
       </c>
       <c r="G97">
-        <v>-9.555940507957704</v>
+        <v>-13.25945442383146</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.480634578649157</v>
       </c>
       <c r="E98">
-        <v>-40.9569270932577</v>
+        <v>-43.36529636780901</v>
       </c>
       <c r="F98">
-        <v>-3.384304283426319</v>
+        <v>-3.86955031084263</v>
       </c>
       <c r="G98">
-        <v>-9.795177081353136</v>
+        <v>-13.04566270345087</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.738374505396237</v>
       </c>
       <c r="E99">
-        <v>-43.15697524227115</v>
+        <v>-45.24521763227223</v>
       </c>
       <c r="F99">
-        <v>-3.482793025782166</v>
+        <v>-4.087007522853736</v>
       </c>
       <c r="G99">
-        <v>-9.720040939793838</v>
+        <v>-13.76060811811187</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.934650139813716</v>
       </c>
       <c r="E100">
-        <v>-44.77669944720165</v>
+        <v>-46.70931629945513</v>
       </c>
       <c r="F100">
-        <v>-3.677697106884653</v>
+        <v>-4.195791215291576</v>
       </c>
       <c r="G100">
-        <v>-10.00932303010643</v>
+        <v>-14.17637291129786</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.065909594704729</v>
       </c>
       <c r="E101">
-        <v>-47.11393771627748</v>
+        <v>-48.76326229155912</v>
       </c>
       <c r="F101">
-        <v>-3.676479406802538</v>
+        <v>-4.460838962960917</v>
       </c>
       <c r="G101">
-        <v>-10.91690577915209</v>
+        <v>-14.10243849776932</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.120152148329181</v>
       </c>
       <c r="E102">
-        <v>-49.22805241040288</v>
+        <v>-50.91943405591226</v>
       </c>
       <c r="F102">
-        <v>-3.832615065086606</v>
+        <v>-4.589249164273285</v>
       </c>
       <c r="G102">
-        <v>-10.95726795036688</v>
+        <v>-14.09037818036975</v>
       </c>
     </row>
   </sheetData>
